--- a/informes_data/Euroleague/2025-26/Regular_Season/individual/NP_play_by_play_EL_315_R32.xlsx
+++ b/informes_data/Euroleague/2025-26/Regular_Season/individual/NP_play_by_play_EL_315_R32.xlsx
@@ -553,7 +553,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>N. SAKO</t>
+          <t>B. KEY</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
@@ -565,67 +565,67 @@
         <v>1</v>
       </c>
       <c r="D2" t="n">
-        <v>3.1093</v>
+        <v>2.6007</v>
       </c>
       <c r="E2" t="n">
-        <v>1.6379</v>
+        <v>1.5921</v>
       </c>
       <c r="F2" t="n">
-        <v>1.4714</v>
+        <v>1.0086</v>
       </c>
       <c r="G2" t="n">
-        <v>1.9371</v>
+        <v>1.6891</v>
       </c>
       <c r="H2" t="n">
-        <v>1.1307</v>
+        <v>1.2642</v>
       </c>
       <c r="I2" t="n">
-        <v>0.8064</v>
+        <v>0.425</v>
       </c>
       <c r="J2" t="n">
-        <v>1.4586</v>
+        <v>1.2853</v>
       </c>
       <c r="K2" t="n">
-        <v>1.385</v>
+        <v>0.8571</v>
       </c>
       <c r="L2" t="n">
-        <v>0.0736</v>
+        <v>0.4282</v>
       </c>
       <c r="M2" t="n">
-        <v>0.4785</v>
+        <v>0.4039</v>
       </c>
       <c r="N2" t="n">
-        <v>-0.2543</v>
+        <v>0.4071</v>
       </c>
       <c r="O2" t="n">
-        <v>0.7328</v>
+        <v>-0.0033</v>
       </c>
       <c r="P2" t="n">
-        <v>0.232</v>
+        <v>1.3917</v>
       </c>
       <c r="Q2" t="n">
-        <v>-1.1598</v>
+        <v>0</v>
       </c>
       <c r="R2" t="n">
         <v>1.3917</v>
       </c>
       <c r="S2" t="n">
-        <v>1.4453</v>
+        <v>-0.1966</v>
       </c>
       <c r="T2" t="n">
-        <v>1.8442</v>
+        <v>0.3068</v>
       </c>
       <c r="U2" t="n">
-        <v>-0.3989</v>
+        <v>-0.5034</v>
       </c>
       <c r="V2" t="n">
-        <v>-0.5051</v>
+        <v>-0.2836</v>
       </c>
       <c r="W2" t="n">
-        <v>-0.5051</v>
+        <v>0</v>
       </c>
       <c r="X2" t="n">
-        <v>0</v>
+        <v>-0.2836</v>
       </c>
     </row>
     <row r="3">
@@ -643,13 +643,13 @@
         <v>1</v>
       </c>
       <c r="D3" t="n">
-        <v>2.7929</v>
+        <v>2.474</v>
       </c>
       <c r="E3" t="n">
-        <v>1.8194</v>
+        <v>1.9373</v>
       </c>
       <c r="F3" t="n">
-        <v>0.9735</v>
+        <v>0.5366</v>
       </c>
       <c r="G3" t="n">
         <v>2.4361</v>
@@ -688,13 +688,13 @@
         <v>1.3917</v>
       </c>
       <c r="S3" t="n">
-        <v>-0.6611</v>
+        <v>-0.9801</v>
       </c>
       <c r="T3" t="n">
-        <v>-0.7389</v>
+        <v>-0.621</v>
       </c>
       <c r="U3" t="n">
-        <v>0.07779999999999999</v>
+        <v>-0.3591</v>
       </c>
       <c r="V3" t="n">
         <v>-0.1418</v>
@@ -709,7 +709,7 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>B. KEY</t>
+          <t>N. SAKO</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
@@ -721,67 +721,67 @@
         <v>1</v>
       </c>
       <c r="D4" t="n">
-        <v>1.7271</v>
+        <v>1.894</v>
       </c>
       <c r="E4" t="n">
-        <v>0.853</v>
+        <v>0.4898</v>
       </c>
       <c r="F4" t="n">
-        <v>0.8741</v>
+        <v>1.4041</v>
       </c>
       <c r="G4" t="n">
-        <v>1.6891</v>
+        <v>1.9371</v>
       </c>
       <c r="H4" t="n">
-        <v>1.2642</v>
+        <v>1.1307</v>
       </c>
       <c r="I4" t="n">
-        <v>0.425</v>
+        <v>0.8064</v>
       </c>
       <c r="J4" t="n">
-        <v>1.2853</v>
+        <v>1.4586</v>
       </c>
       <c r="K4" t="n">
-        <v>0.8571</v>
+        <v>1.385</v>
       </c>
       <c r="L4" t="n">
-        <v>0.4282</v>
+        <v>0.0736</v>
       </c>
       <c r="M4" t="n">
-        <v>0.4039</v>
+        <v>0.4785</v>
       </c>
       <c r="N4" t="n">
-        <v>0.4071</v>
+        <v>-0.2543</v>
       </c>
       <c r="O4" t="n">
-        <v>-0.0033</v>
+        <v>0.7328</v>
       </c>
       <c r="P4" t="n">
-        <v>1.3917</v>
+        <v>0.232</v>
       </c>
       <c r="Q4" t="n">
-        <v>0</v>
+        <v>-1.1598</v>
       </c>
       <c r="R4" t="n">
         <v>1.3917</v>
       </c>
       <c r="S4" t="n">
-        <v>-1.0701</v>
+        <v>0.23</v>
       </c>
       <c r="T4" t="n">
-        <v>-0.4323</v>
+        <v>0.6961000000000001</v>
       </c>
       <c r="U4" t="n">
-        <v>-0.6379</v>
+        <v>-0.4661</v>
       </c>
       <c r="V4" t="n">
-        <v>-0.2836</v>
+        <v>-0.5051</v>
       </c>
       <c r="W4" t="n">
-        <v>0</v>
+        <v>-0.5051</v>
       </c>
       <c r="X4" t="n">
-        <v>-0.2836</v>
+        <v>0</v>
       </c>
     </row>
     <row r="5">
@@ -799,13 +799,13 @@
         <v>1</v>
       </c>
       <c r="D5" t="n">
-        <v>0.7372</v>
+        <v>1.1082</v>
       </c>
       <c r="E5" t="n">
-        <v>-0.1914</v>
+        <v>0.2804</v>
       </c>
       <c r="F5" t="n">
-        <v>0.9286</v>
+        <v>0.8278</v>
       </c>
       <c r="G5" t="n">
         <v>0.5014</v>
@@ -844,13 +844,13 @@
         <v>1.3917</v>
       </c>
       <c r="S5" t="n">
-        <v>-1.7462</v>
+        <v>-1.3752</v>
       </c>
       <c r="T5" t="n">
-        <v>-0.5149</v>
+        <v>-0.0431</v>
       </c>
       <c r="U5" t="n">
-        <v>-1.2313</v>
+        <v>-1.3322</v>
       </c>
       <c r="V5" t="n">
         <v>1.7501</v>
@@ -877,13 +877,13 @@
         <v>1</v>
       </c>
       <c r="D6" t="n">
-        <v>-0.4423</v>
+        <v>0.3634</v>
       </c>
       <c r="E6" t="n">
-        <v>-0.0428</v>
+        <v>0.4604</v>
       </c>
       <c r="F6" t="n">
-        <v>-0.3995</v>
+        <v>-0.09710000000000001</v>
       </c>
       <c r="G6" t="n">
         <v>0.8171</v>
@@ -922,13 +922,13 @@
         <v>0.4639</v>
       </c>
       <c r="S6" t="n">
-        <v>-0.7929</v>
+        <v>0.0127</v>
       </c>
       <c r="T6" t="n">
-        <v>-0.3655</v>
+        <v>0.1377</v>
       </c>
       <c r="U6" t="n">
-        <v>-0.4274</v>
+        <v>-0.125</v>
       </c>
       <c r="V6" t="n">
         <v>-0.9304</v>
@@ -955,13 +955,13 @@
         <v>1</v>
       </c>
       <c r="D7" t="n">
-        <v>-0.7089</v>
+        <v>-0.2713</v>
       </c>
       <c r="E7" t="n">
-        <v>-1.1473</v>
+        <v>-0.9114</v>
       </c>
       <c r="F7" t="n">
-        <v>0.4384</v>
+        <v>0.6401</v>
       </c>
       <c r="G7" t="n">
         <v>0.9146</v>
@@ -1000,13 +1000,13 @@
         <v>1.8556</v>
       </c>
       <c r="S7" t="n">
-        <v>-1.8038</v>
+        <v>-1.3662</v>
       </c>
       <c r="T7" t="n">
-        <v>-0.8136</v>
+        <v>-0.5777</v>
       </c>
       <c r="U7" t="n">
-        <v>-0.9902</v>
+        <v>-0.7885</v>
       </c>
       <c r="V7" t="n">
         <v>-0.2836</v>
@@ -1033,13 +1033,13 @@
         <v>1</v>
       </c>
       <c r="D8" t="n">
-        <v>-0.718</v>
+        <v>-0.7030999999999999</v>
       </c>
       <c r="E8" t="n">
-        <v>-3.0114</v>
+        <v>-2.862</v>
       </c>
       <c r="F8" t="n">
-        <v>2.2933</v>
+        <v>2.1589</v>
       </c>
       <c r="G8" t="n">
         <v>1.0291</v>
@@ -1078,13 +1078,13 @@
         <v>1.1598</v>
       </c>
       <c r="S8" t="n">
-        <v>0.2012</v>
+        <v>0.2161</v>
       </c>
       <c r="T8" t="n">
-        <v>0.3541</v>
+        <v>0.5034</v>
       </c>
       <c r="U8" t="n">
-        <v>-0.1529</v>
+        <v>-0.2873</v>
       </c>
       <c r="V8" t="n">
         <v>-0.7886</v>
@@ -1111,13 +1111,13 @@
         <v>1</v>
       </c>
       <c r="D9" t="n">
-        <v>-0.873</v>
+        <v>-0.9231</v>
       </c>
       <c r="E9" t="n">
-        <v>-0.8527</v>
+        <v>-0.7347</v>
       </c>
       <c r="F9" t="n">
-        <v>-0.0204</v>
+        <v>-0.1884</v>
       </c>
       <c r="G9" t="n">
         <v>0.0412</v>
@@ -1156,13 +1156,13 @@
         <v>1.6237</v>
       </c>
       <c r="S9" t="n">
-        <v>-1.1461</v>
+        <v>-1.1962</v>
       </c>
       <c r="T9" t="n">
-        <v>-0.7389</v>
+        <v>-0.621</v>
       </c>
       <c r="U9" t="n">
-        <v>-0.4072</v>
+        <v>-0.5753</v>
       </c>
       <c r="V9" t="n">
         <v>0</v>
@@ -1177,7 +1177,7 @@
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>N. REUVERS</t>
+          <t>S. DE LARREA</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
@@ -1189,64 +1189,64 @@
         <v>1</v>
       </c>
       <c r="D10" t="n">
-        <v>-2.2795</v>
+        <v>-2.128</v>
       </c>
       <c r="E10" t="n">
-        <v>-2.297</v>
+        <v>-1.733</v>
       </c>
       <c r="F10" t="n">
-        <v>0.0175</v>
+        <v>-0.395</v>
       </c>
       <c r="G10" t="n">
-        <v>-1.2326</v>
+        <v>-1.1422</v>
       </c>
       <c r="H10" t="n">
-        <v>0.6712</v>
+        <v>0.0289</v>
       </c>
       <c r="I10" t="n">
-        <v>-1.9038</v>
+        <v>-1.1711</v>
       </c>
       <c r="J10" t="n">
-        <v>-0.8037</v>
+        <v>-0.6991000000000001</v>
       </c>
       <c r="K10" t="n">
-        <v>0.6218</v>
+        <v>0.0504</v>
       </c>
       <c r="L10" t="n">
-        <v>-1.4255</v>
+        <v>-0.7495000000000001</v>
       </c>
       <c r="M10" t="n">
-        <v>-0.4289</v>
+        <v>-0.4431</v>
       </c>
       <c r="N10" t="n">
-        <v>0.0495</v>
+        <v>-0.0216</v>
       </c>
       <c r="O10" t="n">
-        <v>-0.4783</v>
+        <v>-0.4216</v>
       </c>
       <c r="P10" t="n">
+        <v>-0.6959</v>
+      </c>
+      <c r="Q10" t="n">
         <v>-1.1598</v>
       </c>
-      <c r="Q10" t="n">
-        <v>-2.5515</v>
-      </c>
       <c r="R10" t="n">
-        <v>1.3917</v>
+        <v>0.4639</v>
       </c>
       <c r="S10" t="n">
-        <v>-0.029</v>
+        <v>-0.2899</v>
       </c>
       <c r="T10" t="n">
-        <v>0.9164</v>
+        <v>0.1259</v>
       </c>
       <c r="U10" t="n">
-        <v>-0.9454</v>
+        <v>-0.4158</v>
       </c>
       <c r="V10" t="n">
-        <v>0.1418</v>
+        <v>0</v>
       </c>
       <c r="W10" t="n">
-        <v>0.1418</v>
+        <v>0</v>
       </c>
       <c r="X10" t="n">
         <v>0</v>
@@ -1255,7 +1255,7 @@
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>S. DE LARREA</t>
+          <t>N. REUVERS</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
@@ -1267,64 +1267,64 @@
         <v>1</v>
       </c>
       <c r="D11" t="n">
-        <v>-2.2796</v>
+        <v>-2.9543</v>
       </c>
       <c r="E11" t="n">
-        <v>-1.851</v>
+        <v>-3.2406</v>
       </c>
       <c r="F11" t="n">
-        <v>-0.4286</v>
+        <v>0.2863</v>
       </c>
       <c r="G11" t="n">
-        <v>-1.1422</v>
+        <v>-1.2326</v>
       </c>
       <c r="H11" t="n">
-        <v>0.0289</v>
+        <v>0.6712</v>
       </c>
       <c r="I11" t="n">
-        <v>-1.1711</v>
+        <v>-1.9038</v>
       </c>
       <c r="J11" t="n">
-        <v>-0.6991000000000001</v>
+        <v>-0.8037</v>
       </c>
       <c r="K11" t="n">
-        <v>0.0504</v>
+        <v>0.6218</v>
       </c>
       <c r="L11" t="n">
-        <v>-0.7495000000000001</v>
+        <v>-1.4255</v>
       </c>
       <c r="M11" t="n">
-        <v>-0.4431</v>
+        <v>-0.4289</v>
       </c>
       <c r="N11" t="n">
-        <v>-0.0216</v>
+        <v>0.0495</v>
       </c>
       <c r="O11" t="n">
-        <v>-0.4216</v>
+        <v>-0.4783</v>
       </c>
       <c r="P11" t="n">
-        <v>-0.6959</v>
+        <v>-1.1598</v>
       </c>
       <c r="Q11" t="n">
-        <v>-1.1598</v>
+        <v>-2.5515</v>
       </c>
       <c r="R11" t="n">
-        <v>0.4639</v>
+        <v>1.3917</v>
       </c>
       <c r="S11" t="n">
-        <v>-0.4415</v>
+        <v>-0.7038</v>
       </c>
       <c r="T11" t="n">
-        <v>0.007900000000000001</v>
+        <v>-0.0272</v>
       </c>
       <c r="U11" t="n">
-        <v>-0.4494</v>
+        <v>-0.6765</v>
       </c>
       <c r="V11" t="n">
-        <v>0</v>
+        <v>0.1418</v>
       </c>
       <c r="W11" t="n">
-        <v>0</v>
+        <v>0.1418</v>
       </c>
       <c r="X11" t="n">
         <v>0</v>
@@ -1345,13 +1345,13 @@
         <v>1</v>
       </c>
       <c r="D12" t="n">
-        <v>-5.5732</v>
+        <v>-5.2215</v>
       </c>
       <c r="E12" t="n">
-        <v>-6.6562</v>
+        <v>-6.2709</v>
       </c>
       <c r="F12" t="n">
-        <v>1.083</v>
+        <v>1.0494</v>
       </c>
       <c r="G12" t="n">
         <v>-4.167</v>
@@ -1390,13 +1390,13 @@
         <v>1.3917</v>
       </c>
       <c r="S12" t="n">
-        <v>-0.2464</v>
+        <v>0.1052</v>
       </c>
       <c r="T12" t="n">
-        <v>-0.6563</v>
+        <v>-0.2711</v>
       </c>
       <c r="U12" t="n">
-        <v>0.4099</v>
+        <v>0.3763</v>
       </c>
       <c r="V12" t="n">
         <v>0</v>
@@ -1423,16 +1423,16 @@
         <v>1</v>
       </c>
       <c r="D13" t="n">
-        <v>-4.508</v>
+        <v>-3.760999999999999</v>
       </c>
       <c r="E13" t="n">
-        <v>-11.7395</v>
+        <v>-10.9926</v>
       </c>
       <c r="F13" t="n">
         <v>7.2313</v>
       </c>
       <c r="G13" t="n">
-        <v>2.823900000000001</v>
+        <v>2.8239</v>
       </c>
       <c r="H13" t="n">
         <v>7.023200000000001</v>
@@ -1441,10 +1441,10 @@
         <v>-4.199299999999999</v>
       </c>
       <c r="J13" t="n">
-        <v>2.575700000000001</v>
+        <v>2.5757</v>
       </c>
       <c r="K13" t="n">
-        <v>8.0474</v>
+        <v>8.047399999999998</v>
       </c>
       <c r="L13" t="n">
         <v>-5.4718</v>
@@ -1468,10 +1468,10 @@
         <v>13.9171</v>
       </c>
       <c r="S13" t="n">
-        <v>-6.2906</v>
+        <v>-5.544</v>
       </c>
       <c r="T13" t="n">
-        <v>-1.1378</v>
+        <v>-0.3912</v>
       </c>
       <c r="U13" t="n">
         <v>-5.1529</v>
@@ -1501,13 +1501,13 @@
         <v>1</v>
       </c>
       <c r="D14" t="n">
-        <v>6.1397</v>
+        <v>4.7199</v>
       </c>
       <c r="E14" t="n">
-        <v>2.9352</v>
+        <v>1.6378</v>
       </c>
       <c r="F14" t="n">
-        <v>3.2045</v>
+        <v>3.0821</v>
       </c>
       <c r="G14" t="n">
         <v>0.8147</v>
@@ -1546,13 +1546,13 @@
         <v>2.3195</v>
       </c>
       <c r="S14" t="n">
-        <v>2.5905</v>
+        <v>1.1707</v>
       </c>
       <c r="T14" t="n">
-        <v>1.9663</v>
+        <v>0.6688</v>
       </c>
       <c r="U14" t="n">
-        <v>0.6243</v>
+        <v>0.5019</v>
       </c>
       <c r="V14" t="n">
         <v>0.6468</v>
@@ -1567,7 +1567,7 @@
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>M. NORRIS</t>
+          <t>J. VESELY</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
@@ -1579,58 +1579,58 @@
         <v>1</v>
       </c>
       <c r="D15" t="n">
-        <v>3.5721</v>
+        <v>2.8684</v>
       </c>
       <c r="E15" t="n">
-        <v>2.5884</v>
+        <v>0.2489</v>
       </c>
       <c r="F15" t="n">
-        <v>0.9838</v>
+        <v>2.6195</v>
       </c>
       <c r="G15" t="n">
-        <v>0.0924</v>
+        <v>1.3342</v>
       </c>
       <c r="H15" t="n">
-        <v>0.4705</v>
+        <v>0.2232</v>
       </c>
       <c r="I15" t="n">
-        <v>-0.3781</v>
+        <v>1.1109</v>
       </c>
       <c r="J15" t="n">
-        <v>0.2214</v>
+        <v>1.1842</v>
       </c>
       <c r="K15" t="n">
-        <v>0.8605</v>
+        <v>0.6456</v>
       </c>
       <c r="L15" t="n">
-        <v>-0.6391</v>
+        <v>0.5386</v>
       </c>
       <c r="M15" t="n">
-        <v>-0.129</v>
+        <v>0.15</v>
       </c>
       <c r="N15" t="n">
-        <v>-0.39</v>
+        <v>-0.4223</v>
       </c>
       <c r="O15" t="n">
-        <v>0.261</v>
+        <v>0.5723</v>
       </c>
       <c r="P15" t="n">
-        <v>0.4639</v>
+        <v>0.6959</v>
       </c>
       <c r="Q15" t="n">
-        <v>0</v>
+        <v>-1.1598</v>
       </c>
       <c r="R15" t="n">
-        <v>0.4639</v>
+        <v>1.8556</v>
       </c>
       <c r="S15" t="n">
-        <v>3.0158</v>
+        <v>0.8384</v>
       </c>
       <c r="T15" t="n">
-        <v>2.3669</v>
+        <v>0.2245</v>
       </c>
       <c r="U15" t="n">
-        <v>0.6489</v>
+        <v>0.6139</v>
       </c>
       <c r="V15" t="n">
         <v>0</v>
@@ -1645,7 +1645,7 @@
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>J. VESELY</t>
+          <t>M. NORRIS</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
@@ -1657,58 +1657,58 @@
         <v>1</v>
       </c>
       <c r="D16" t="n">
-        <v>1.744</v>
+        <v>2.3146</v>
       </c>
       <c r="E16" t="n">
-        <v>-0.9306</v>
+        <v>1.4088</v>
       </c>
       <c r="F16" t="n">
-        <v>2.6746</v>
+        <v>0.9058</v>
       </c>
       <c r="G16" t="n">
-        <v>1.3342</v>
+        <v>0.0924</v>
       </c>
       <c r="H16" t="n">
-        <v>0.2232</v>
+        <v>0.4705</v>
       </c>
       <c r="I16" t="n">
-        <v>1.1109</v>
+        <v>-0.3781</v>
       </c>
       <c r="J16" t="n">
-        <v>1.1842</v>
+        <v>0.2214</v>
       </c>
       <c r="K16" t="n">
-        <v>0.6456</v>
+        <v>0.8605</v>
       </c>
       <c r="L16" t="n">
-        <v>0.5386</v>
+        <v>-0.6391</v>
       </c>
       <c r="M16" t="n">
-        <v>0.15</v>
+        <v>-0.129</v>
       </c>
       <c r="N16" t="n">
-        <v>-0.4223</v>
+        <v>-0.39</v>
       </c>
       <c r="O16" t="n">
-        <v>0.5723</v>
+        <v>0.261</v>
       </c>
       <c r="P16" t="n">
-        <v>0.6959</v>
+        <v>0.4639</v>
       </c>
       <c r="Q16" t="n">
-        <v>-1.1598</v>
+        <v>0</v>
       </c>
       <c r="R16" t="n">
-        <v>1.8556</v>
+        <v>0.4639</v>
       </c>
       <c r="S16" t="n">
-        <v>-0.286</v>
+        <v>1.7583</v>
       </c>
       <c r="T16" t="n">
-        <v>-0.955</v>
+        <v>1.1874</v>
       </c>
       <c r="U16" t="n">
-        <v>0.6691</v>
+        <v>0.5709</v>
       </c>
       <c r="V16" t="n">
         <v>0</v>
@@ -1735,13 +1735,13 @@
         <v>1</v>
       </c>
       <c r="D17" t="n">
-        <v>1.1935</v>
+        <v>2.0192</v>
       </c>
       <c r="E17" t="n">
-        <v>0.1662</v>
+        <v>0.52</v>
       </c>
       <c r="F17" t="n">
-        <v>1.0274</v>
+        <v>1.4992</v>
       </c>
       <c r="G17" t="n">
         <v>0.9334</v>
@@ -1780,13 +1780,13 @@
         <v>1.6237</v>
       </c>
       <c r="S17" t="n">
-        <v>0.5306999999999999</v>
+        <v>1.3563</v>
       </c>
       <c r="T17" t="n">
-        <v>0.2047</v>
+        <v>0.5586</v>
       </c>
       <c r="U17" t="n">
-        <v>0.326</v>
+        <v>0.7978</v>
       </c>
       <c r="V17" t="n">
         <v>0.4254</v>
@@ -1813,13 +1813,13 @@
         <v>1</v>
       </c>
       <c r="D18" t="n">
-        <v>1.1035</v>
+        <v>1.5638</v>
       </c>
       <c r="E18" t="n">
-        <v>0.153</v>
+        <v>0.3889</v>
       </c>
       <c r="F18" t="n">
-        <v>0.9505</v>
+        <v>1.1749</v>
       </c>
       <c r="G18" t="n">
         <v>0.0381</v>
@@ -1858,13 +1858,13 @@
         <v>0.4639</v>
       </c>
       <c r="S18" t="n">
-        <v>-0.1871</v>
+        <v>0.2732</v>
       </c>
       <c r="T18" t="n">
-        <v>0.08260000000000001</v>
+        <v>0.3185</v>
       </c>
       <c r="U18" t="n">
-        <v>-0.2697</v>
+        <v>-0.0452</v>
       </c>
       <c r="V18" t="n">
         <v>0.7886</v>
@@ -1891,13 +1891,13 @@
         <v>1</v>
       </c>
       <c r="D19" t="n">
-        <v>0.2685</v>
+        <v>0.6775</v>
       </c>
       <c r="E19" t="n">
-        <v>-1.1896</v>
+        <v>-1.3076</v>
       </c>
       <c r="F19" t="n">
-        <v>1.4581</v>
+        <v>1.9851</v>
       </c>
       <c r="G19" t="n">
         <v>0.2971</v>
@@ -1936,13 +1936,13 @@
         <v>1.6237</v>
       </c>
       <c r="S19" t="n">
-        <v>0.6673</v>
+        <v>1.0763</v>
       </c>
       <c r="T19" t="n">
-        <v>0.9006</v>
+        <v>0.7826</v>
       </c>
       <c r="U19" t="n">
-        <v>-0.2333</v>
+        <v>0.2937</v>
       </c>
       <c r="V19" t="n">
         <v>0</v>
@@ -1957,7 +1957,7 @@
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>M. CALE</t>
+          <t>T. SATORANSKY</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
@@ -1969,73 +1969,73 @@
         <v>1</v>
       </c>
       <c r="D20" t="n">
-        <v>-0.1147</v>
+        <v>0.249</v>
       </c>
       <c r="E20" t="n">
-        <v>-0.1061</v>
+        <v>-0.3755</v>
       </c>
       <c r="F20" t="n">
-        <v>-0.0086</v>
+        <v>0.6245000000000001</v>
       </c>
       <c r="G20" t="n">
-        <v>-0.2186</v>
+        <v>1.3749</v>
       </c>
       <c r="H20" t="n">
-        <v>-1.4633</v>
+        <v>1.0001</v>
       </c>
       <c r="I20" t="n">
-        <v>1.2447</v>
+        <v>0.3748</v>
       </c>
       <c r="J20" t="n">
-        <v>-0.0788</v>
+        <v>1.5503</v>
       </c>
       <c r="K20" t="n">
-        <v>-0.4334</v>
+        <v>1.7477</v>
       </c>
       <c r="L20" t="n">
-        <v>0.3546</v>
+        <v>-0.1975</v>
       </c>
       <c r="M20" t="n">
-        <v>-0.1398</v>
+        <v>-0.1754</v>
       </c>
       <c r="N20" t="n">
-        <v>-1.0299</v>
+        <v>-0.7477</v>
       </c>
       <c r="O20" t="n">
-        <v>0.8901</v>
+        <v>0.5723</v>
       </c>
       <c r="P20" t="n">
-        <v>0.9278</v>
+        <v>-0.6959</v>
       </c>
       <c r="Q20" t="n">
-        <v>-0.232</v>
+        <v>-2.3195</v>
       </c>
       <c r="R20" t="n">
-        <v>1.1598</v>
+        <v>1.6237</v>
       </c>
       <c r="S20" t="n">
-        <v>0.3901</v>
+        <v>0.5004</v>
       </c>
       <c r="T20" t="n">
-        <v>0.2047</v>
+        <v>0.2519</v>
       </c>
       <c r="U20" t="n">
-        <v>0.1854</v>
+        <v>0.2484</v>
       </c>
       <c r="V20" t="n">
-        <v>-1.214</v>
+        <v>-0.9304</v>
       </c>
       <c r="W20" t="n">
-        <v>0</v>
+        <v>0.1418</v>
       </c>
       <c r="X20" t="n">
-        <v>-1.214</v>
+        <v>-1.0722</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>T. SATORANSKY</t>
+          <t>M. CALE</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
@@ -2047,67 +2047,67 @@
         <v>1</v>
       </c>
       <c r="D21" t="n">
-        <v>-0.8563</v>
+        <v>-0.1311</v>
       </c>
       <c r="E21" t="n">
-        <v>-0.7294</v>
+        <v>0.0119</v>
       </c>
       <c r="F21" t="n">
-        <v>-0.1269</v>
+        <v>-0.143</v>
       </c>
       <c r="G21" t="n">
-        <v>1.3749</v>
+        <v>-0.2186</v>
       </c>
       <c r="H21" t="n">
-        <v>1.0001</v>
+        <v>-1.4633</v>
       </c>
       <c r="I21" t="n">
-        <v>0.3748</v>
+        <v>1.2447</v>
       </c>
       <c r="J21" t="n">
-        <v>1.5503</v>
+        <v>-0.0788</v>
       </c>
       <c r="K21" t="n">
-        <v>1.7477</v>
+        <v>-0.4334</v>
       </c>
       <c r="L21" t="n">
-        <v>-0.1975</v>
+        <v>0.3546</v>
       </c>
       <c r="M21" t="n">
-        <v>-0.1754</v>
+        <v>-0.1398</v>
       </c>
       <c r="N21" t="n">
-        <v>-0.7477</v>
+        <v>-1.0299</v>
       </c>
       <c r="O21" t="n">
-        <v>0.5723</v>
+        <v>0.8901</v>
       </c>
       <c r="P21" t="n">
-        <v>-0.6959</v>
+        <v>0.9278</v>
       </c>
       <c r="Q21" t="n">
-        <v>-2.3195</v>
+        <v>-0.232</v>
       </c>
       <c r="R21" t="n">
-        <v>1.6237</v>
+        <v>1.1598</v>
       </c>
       <c r="S21" t="n">
-        <v>-0.6049</v>
+        <v>0.3736</v>
       </c>
       <c r="T21" t="n">
-        <v>-0.1019</v>
+        <v>0.3227</v>
       </c>
       <c r="U21" t="n">
-        <v>-0.503</v>
+        <v>0.051</v>
       </c>
       <c r="V21" t="n">
-        <v>-0.9304</v>
+        <v>-1.214</v>
       </c>
       <c r="W21" t="n">
-        <v>0.1418</v>
+        <v>0</v>
       </c>
       <c r="X21" t="n">
-        <v>-1.0722</v>
+        <v>-1.214</v>
       </c>
     </row>
     <row r="22">
@@ -2125,13 +2125,13 @@
         <v>1</v>
       </c>
       <c r="D22" t="n">
-        <v>-1.3986</v>
+        <v>-1.1741</v>
       </c>
       <c r="E22" t="n">
         <v>-2.165</v>
       </c>
       <c r="F22" t="n">
-        <v>0.7664</v>
+        <v>0.9909</v>
       </c>
       <c r="G22" t="n">
         <v>-0.4567</v>
@@ -2170,13 +2170,13 @@
         <v>1.1598</v>
       </c>
       <c r="S22" t="n">
-        <v>0.4498</v>
+        <v>0.6743</v>
       </c>
       <c r="T22" t="n">
         <v>0.5034</v>
       </c>
       <c r="U22" t="n">
-        <v>-0.0536</v>
+        <v>0.1709</v>
       </c>
       <c r="V22" t="n">
         <v>0</v>
@@ -2203,13 +2203,13 @@
         <v>1</v>
       </c>
       <c r="D23" t="n">
-        <v>-1.5735</v>
+        <v>-1.2032</v>
       </c>
       <c r="E23" t="n">
-        <v>-0.8164</v>
+        <v>-0.5805</v>
       </c>
       <c r="F23" t="n">
-        <v>-0.7571</v>
+        <v>-0.6227</v>
       </c>
       <c r="G23" t="n">
         <v>-0.8309</v>
@@ -2248,13 +2248,13 @@
         <v>0.4639</v>
       </c>
       <c r="S23" t="n">
-        <v>-0.2091</v>
+        <v>0.1612</v>
       </c>
       <c r="T23" t="n">
-        <v>-0.2987</v>
+        <v>-0.06279999999999999</v>
       </c>
       <c r="U23" t="n">
-        <v>0.0896</v>
+        <v>0.224</v>
       </c>
       <c r="V23" t="n">
         <v>0.3943</v>
@@ -2281,13 +2281,13 @@
         <v>1</v>
       </c>
       <c r="D24" t="n">
-        <v>-5.5703</v>
+        <v>-5.037</v>
       </c>
       <c r="E24" t="n">
-        <v>-7.137</v>
+        <v>-7.019</v>
       </c>
       <c r="F24" t="n">
-        <v>1.5667</v>
+        <v>1.982</v>
       </c>
       <c r="G24" t="n">
         <v>-6.2024</v>
@@ -2326,13 +2326,13 @@
         <v>1.1598</v>
       </c>
       <c r="S24" t="n">
-        <v>-0.0663</v>
+        <v>0.467</v>
       </c>
       <c r="T24" t="n">
-        <v>0.2794</v>
+        <v>0.3973</v>
       </c>
       <c r="U24" t="n">
-        <v>-0.3457</v>
+        <v>0.0696</v>
       </c>
       <c r="V24" t="n">
         <v>0.9304</v>
@@ -2359,13 +2359,13 @@
         <v>1</v>
       </c>
       <c r="D25" t="n">
-        <v>4.507900000000001</v>
+        <v>6.867</v>
       </c>
       <c r="E25" t="n">
         <v>-7.2313</v>
       </c>
       <c r="F25" t="n">
-        <v>11.7394</v>
+        <v>14.0983</v>
       </c>
       <c r="G25" t="n">
         <v>-2.823799999999999</v>
@@ -2404,13 +2404,13 @@
         <v>13.9173</v>
       </c>
       <c r="S25" t="n">
-        <v>6.290799999999999</v>
+        <v>8.649700000000001</v>
       </c>
       <c r="T25" t="n">
-        <v>5.152999999999999</v>
+        <v>5.152899999999999</v>
       </c>
       <c r="U25" t="n">
-        <v>1.138</v>
+        <v>3.4969</v>
       </c>
       <c r="V25" t="n">
         <v>1.0411</v>
